--- a/final_summary.xlsx
+++ b/final_summary.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paula\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paula\OneDrive\Desktop\TER_project-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAF05E1-C017-49E7-933A-365FF0AE6D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13171BC8-EE02-41D7-A692-E65543F0B9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3FA1256-5090-445C-AF8A-7C4B98C96EB0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="summary" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$U$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">summary!$A$1:$U$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -208,25 +208,25 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="2"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -745,52 +745,52 @@
   </cols>
   <sheetData>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="18"/>
-      <c r="N7" s="18"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="18"/>
-      <c r="R7" s="18"/>
-      <c r="S7" s="18"/>
-      <c r="T7" s="18"/>
-      <c r="U7" s="18"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
     </row>
     <row r="9" spans="1:24" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -840,780 +840,780 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19" t="s">
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19" t="s">
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="14"/>
+      <c r="T11" s="14"/>
       <c r="U11" s="1"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="15"/>
+      <c r="T12" s="15"/>
       <c r="U12" s="1"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="15"/>
+      <c r="T13" s="15"/>
       <c r="U13" s="1"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="15"/>
+      <c r="T14" s="15"/>
       <c r="U14" s="1"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="15"/>
       <c r="U15" s="1"/>
       <c r="X15" s="5"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15"/>
+      <c r="R16" s="15"/>
+      <c r="S16" s="15"/>
+      <c r="T16" s="15"/>
       <c r="U16" s="1"/>
       <c r="X16" s="5"/>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="15"/>
       <c r="U17" s="1"/>
       <c r="Y17" s="6"/>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15"/>
+      <c r="R18" s="15"/>
+      <c r="S18" s="15"/>
+      <c r="T18" s="15"/>
       <c r="U18" s="1"/>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="15"/>
+      <c r="R19" s="15"/>
+      <c r="S19" s="15"/>
+      <c r="T19" s="15"/>
       <c r="U19" s="1"/>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="16"/>
-      <c r="T20" s="16"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15"/>
+      <c r="R20" s="15"/>
+      <c r="S20" s="15"/>
+      <c r="T20" s="15"/>
       <c r="U20" s="1"/>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="16"/>
-      <c r="T21" s="16"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="15"/>
+      <c r="R21" s="15"/>
+      <c r="S21" s="15"/>
+      <c r="T21" s="15"/>
       <c r="U21" s="1"/>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
-      <c r="S22" s="16"/>
-      <c r="T22" s="16"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15"/>
+      <c r="R22" s="15"/>
+      <c r="S22" s="15"/>
+      <c r="T22" s="15"/>
       <c r="U22" s="1"/>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="16"/>
-      <c r="S23" s="16"/>
-      <c r="T23" s="16"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15"/>
+      <c r="R23" s="15"/>
+      <c r="S23" s="15"/>
+      <c r="T23" s="15"/>
       <c r="U23" s="1"/>
       <c r="X23" s="8"/>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
-      <c r="T24" s="16"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="15"/>
+      <c r="T24" s="15"/>
       <c r="U24" s="1"/>
       <c r="X24" s="8"/>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16"/>
-      <c r="S25" s="16"/>
-      <c r="T25" s="16"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="15"/>
+      <c r="R25" s="15"/>
+      <c r="S25" s="15"/>
+      <c r="T25" s="15"/>
       <c r="U25" s="1"/>
       <c r="X25" s="8"/>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="16"/>
-      <c r="S26" s="16"/>
-      <c r="T26" s="16"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="15"/>
+      <c r="T26" s="15"/>
       <c r="U26" s="1"/>
       <c r="X26" s="8"/>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
-      <c r="S27" s="16"/>
-      <c r="T27" s="16"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+      <c r="T27" s="15"/>
       <c r="U27" s="1"/>
       <c r="X27" s="9"/>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="15"/>
+      <c r="T28" s="15"/>
       <c r="U28" s="1"/>
       <c r="X28" s="8"/>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="16"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="16"/>
-      <c r="S29" s="16"/>
-      <c r="T29" s="16"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
+      <c r="S29" s="15"/>
+      <c r="T29" s="15"/>
       <c r="U29" s="1"/>
       <c r="X29" s="8"/>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="16"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="16"/>
-      <c r="S30" s="16"/>
-      <c r="T30" s="16"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
+      <c r="R30" s="15"/>
+      <c r="S30" s="15"/>
+      <c r="T30" s="15"/>
       <c r="U30" s="1"/>
       <c r="X30" s="8"/>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="16"/>
-      <c r="S31" s="16"/>
-      <c r="T31" s="16"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
+      <c r="T31" s="15"/>
       <c r="U31" s="1"/>
       <c r="X31" s="8"/>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="16"/>
-      <c r="R32" s="16"/>
-      <c r="S32" s="16"/>
-      <c r="T32" s="16"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="15"/>
+      <c r="T32" s="15"/>
       <c r="U32" s="1"/>
       <c r="X32" s="8"/>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="16"/>
-      <c r="O33" s="16"/>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="16"/>
-      <c r="R33" s="16"/>
-      <c r="S33" s="16"/>
-      <c r="T33" s="16"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="15"/>
+      <c r="T33" s="15"/>
       <c r="U33" s="1"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="16"/>
-      <c r="O34" s="16"/>
-      <c r="P34" s="16"/>
-      <c r="Q34" s="16"/>
-      <c r="R34" s="16"/>
-      <c r="S34" s="16"/>
-      <c r="T34" s="16"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="15"/>
+      <c r="T34" s="15"/>
       <c r="U34" s="1"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="16"/>
-      <c r="O35" s="16"/>
-      <c r="P35" s="16"/>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="16"/>
-      <c r="S35" s="16"/>
-      <c r="T35" s="16"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="15"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="15"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="15"/>
+      <c r="T35" s="15"/>
       <c r="U35" s="1"/>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="16"/>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="16"/>
-      <c r="S36" s="16"/>
-      <c r="T36" s="16"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="15"/>
+      <c r="T36" s="15"/>
       <c r="U36" s="1"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="16"/>
-      <c r="O37" s="16"/>
-      <c r="P37" s="16"/>
-      <c r="Q37" s="16"/>
-      <c r="R37" s="16"/>
-      <c r="S37" s="16"/>
-      <c r="T37" s="16"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="15"/>
+      <c r="P37" s="15"/>
+      <c r="Q37" s="15"/>
+      <c r="R37" s="15"/>
+      <c r="S37" s="15"/>
+      <c r="T37" s="15"/>
       <c r="U37" s="1"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="16"/>
-      <c r="R38" s="16"/>
-      <c r="S38" s="16"/>
-      <c r="T38" s="16"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="15"/>
+      <c r="T38" s="15"/>
       <c r="U38" s="1"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="16"/>
-      <c r="R39" s="16"/>
-      <c r="S39" s="16"/>
-      <c r="T39" s="16"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="15"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="15"/>
+      <c r="R39" s="15"/>
+      <c r="S39" s="15"/>
+      <c r="T39" s="15"/>
       <c r="U39" s="1"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="16"/>
-      <c r="O40" s="16"/>
-      <c r="P40" s="16"/>
-      <c r="Q40" s="16"/>
-      <c r="R40" s="16"/>
-      <c r="S40" s="16"/>
-      <c r="T40" s="16"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="15"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15"/>
+      <c r="R40" s="15"/>
+      <c r="S40" s="15"/>
+      <c r="T40" s="15"/>
       <c r="U40" s="1"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="16"/>
-      <c r="J41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="16"/>
-      <c r="O41" s="16"/>
-      <c r="P41" s="16"/>
-      <c r="Q41" s="16"/>
-      <c r="R41" s="16"/>
-      <c r="S41" s="16"/>
-      <c r="T41" s="16"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="15"/>
+      <c r="O41" s="15"/>
+      <c r="P41" s="15"/>
+      <c r="Q41" s="15"/>
+      <c r="R41" s="15"/>
+      <c r="S41" s="15"/>
+      <c r="T41" s="15"/>
       <c r="U41" s="1"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="16"/>
-      <c r="O42" s="16"/>
-      <c r="P42" s="16"/>
-      <c r="Q42" s="16"/>
-      <c r="R42" s="16"/>
-      <c r="S42" s="16"/>
-      <c r="T42" s="16"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
+      <c r="M42" s="15"/>
+      <c r="N42" s="15"/>
+      <c r="O42" s="15"/>
+      <c r="P42" s="15"/>
+      <c r="Q42" s="15"/>
+      <c r="R42" s="15"/>
+      <c r="S42" s="15"/>
+      <c r="T42" s="15"/>
       <c r="U42" s="1"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
-      <c r="B43" s="16"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
-      <c r="J43" s="16"/>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="16"/>
-      <c r="O43" s="16"/>
-      <c r="P43" s="16"/>
-      <c r="Q43" s="16"/>
-      <c r="R43" s="16"/>
-      <c r="S43" s="16"/>
-      <c r="T43" s="16"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
+      <c r="L43" s="15"/>
+      <c r="M43" s="15"/>
+      <c r="N43" s="15"/>
+      <c r="O43" s="15"/>
+      <c r="P43" s="15"/>
+      <c r="Q43" s="15"/>
+      <c r="R43" s="15"/>
+      <c r="S43" s="15"/>
+      <c r="T43" s="15"/>
       <c r="U43" s="1"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -1647,19 +1647,19 @@
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="12"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
       <c r="J45" s="1"/>
-      <c r="K45" s="12"/>
-      <c r="L45" s="12"/>
-      <c r="M45" s="12"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="13"/>
+      <c r="M45" s="13"/>
       <c r="N45" s="10"/>
-      <c r="O45" s="12"/>
-      <c r="P45" s="12"/>
-      <c r="Q45" s="12"/>
+      <c r="O45" s="13"/>
+      <c r="P45" s="13"/>
+      <c r="Q45" s="13"/>
       <c r="R45" s="1"/>
-      <c r="S45" s="12"/>
-      <c r="T45" s="12"/>
+      <c r="S45" s="13"/>
+      <c r="T45" s="13"/>
       <c r="U45" s="1"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -1673,16 +1673,16 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
-      <c r="M46" s="12"/>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
       <c r="N46" s="10"/>
-      <c r="O46" s="12"/>
-      <c r="P46" s="12"/>
-      <c r="Q46" s="12"/>
+      <c r="O46" s="13"/>
+      <c r="P46" s="13"/>
+      <c r="Q46" s="13"/>
       <c r="R46" s="1"/>
-      <c r="S46" s="12"/>
-      <c r="T46" s="12"/>
+      <c r="S46" s="13"/>
+      <c r="T46" s="13"/>
       <c r="U46" s="1"/>
     </row>
     <row r="47" spans="1:21" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1718,19 +1718,19 @@
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="12"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="13"/>
       <c r="J48" s="1"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-      <c r="M48" s="14"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
       <c r="N48" s="1"/>
-      <c r="O48" s="13"/>
-      <c r="P48" s="13"/>
-      <c r="Q48" s="13"/>
+      <c r="O48" s="18"/>
+      <c r="P48" s="18"/>
+      <c r="Q48" s="18"/>
       <c r="R48" s="1"/>
-      <c r="S48" s="15"/>
-      <c r="T48" s="15"/>
+      <c r="S48" s="19"/>
+      <c r="T48" s="19"/>
       <c r="U48" s="1"/>
     </row>
     <row r="49" spans="1:21" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1743,19 +1743,19 @@
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="12"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="13"/>
       <c r="J49" s="1"/>
-      <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
-      <c r="M49" s="14"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
       <c r="N49" s="1"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="13"/>
-      <c r="Q49" s="13"/>
+      <c r="O49" s="18"/>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="18"/>
       <c r="R49" s="1"/>
-      <c r="S49" s="14"/>
-      <c r="T49" s="14"/>
+      <c r="S49" s="17"/>
+      <c r="T49" s="17"/>
       <c r="U49" s="1"/>
     </row>
     <row r="50" spans="1:21" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1768,19 +1768,19 @@
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="12"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="13"/>
       <c r="J50" s="1"/>
-      <c r="K50" s="14"/>
-      <c r="L50" s="14"/>
-      <c r="M50" s="14"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
       <c r="N50" s="1"/>
-      <c r="O50" s="13"/>
-      <c r="P50" s="13"/>
-      <c r="Q50" s="13"/>
+      <c r="O50" s="18"/>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="18"/>
       <c r="R50" s="1"/>
-      <c r="S50" s="14"/>
-      <c r="T50" s="14"/>
+      <c r="S50" s="17"/>
+      <c r="T50" s="17"/>
       <c r="U50" s="1"/>
     </row>
     <row r="51" spans="1:21" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1793,19 +1793,19 @@
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="12"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="13"/>
       <c r="J51" s="1"/>
-      <c r="K51" s="14"/>
-      <c r="L51" s="14"/>
-      <c r="M51" s="14"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="17"/>
+      <c r="M51" s="17"/>
       <c r="N51" s="1"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="13"/>
+      <c r="O51" s="18"/>
+      <c r="P51" s="18"/>
+      <c r="Q51" s="18"/>
       <c r="R51" s="1"/>
-      <c r="S51" s="14"/>
-      <c r="T51" s="14"/>
+      <c r="S51" s="17"/>
+      <c r="T51" s="17"/>
       <c r="U51" s="1"/>
     </row>
     <row r="52" spans="1:21" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1843,19 +1843,19 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="12"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="13"/>
       <c r="J53" s="1"/>
-      <c r="K53" s="12"/>
-      <c r="L53" s="12"/>
-      <c r="M53" s="12"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="13"/>
       <c r="N53" s="1"/>
-      <c r="O53" s="13"/>
-      <c r="P53" s="13"/>
-      <c r="Q53" s="13"/>
+      <c r="O53" s="18"/>
+      <c r="P53" s="18"/>
+      <c r="Q53" s="18"/>
       <c r="R53" s="1"/>
-      <c r="S53" s="12"/>
-      <c r="T53" s="12"/>
+      <c r="S53" s="13"/>
+      <c r="T53" s="13"/>
       <c r="U53" s="1"/>
     </row>
     <row r="54" spans="1:21" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1868,19 +1868,19 @@
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
       <c r="J54" s="1"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
-      <c r="M54" s="12"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
       <c r="N54" s="1"/>
-      <c r="O54" s="13"/>
-      <c r="P54" s="13"/>
-      <c r="Q54" s="13"/>
+      <c r="O54" s="18"/>
+      <c r="P54" s="18"/>
+      <c r="Q54" s="18"/>
       <c r="R54" s="1"/>
-      <c r="S54" s="12"/>
-      <c r="T54" s="12"/>
+      <c r="S54" s="13"/>
+      <c r="T54" s="13"/>
       <c r="U54" s="1"/>
     </row>
     <row r="55" spans="1:21" ht="14.1" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2107,111 +2107,18 @@
     </row>
   </sheetData>
   <mergeCells count="132">
-    <mergeCell ref="A7:U7"/>
-    <mergeCell ref="A8:U8"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="I11:N11"/>
-    <mergeCell ref="O11:T11"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="I12:N12"/>
-    <mergeCell ref="O12:T12"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="I15:N15"/>
-    <mergeCell ref="O15:T15"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="I16:N16"/>
-    <mergeCell ref="O16:T16"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="O13:T13"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="I14:N14"/>
-    <mergeCell ref="O14:T14"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="O19:T19"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="I20:N20"/>
-    <mergeCell ref="O20:T20"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="I17:N17"/>
-    <mergeCell ref="O17:T17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="I18:N18"/>
-    <mergeCell ref="O18:T18"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="I23:N23"/>
-    <mergeCell ref="O23:T23"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="I24:N24"/>
-    <mergeCell ref="O24:T24"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="I21:N21"/>
-    <mergeCell ref="O21:T21"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="I22:N22"/>
-    <mergeCell ref="O22:T22"/>
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="I27:N27"/>
-    <mergeCell ref="O27:T27"/>
-    <mergeCell ref="B28:H28"/>
-    <mergeCell ref="I28:N28"/>
-    <mergeCell ref="O28:T28"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="I25:N25"/>
-    <mergeCell ref="O25:T25"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="I26:N26"/>
-    <mergeCell ref="O26:T26"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="I31:N31"/>
-    <mergeCell ref="O31:T31"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="I32:N32"/>
-    <mergeCell ref="O32:T32"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="I29:N29"/>
-    <mergeCell ref="O29:T29"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="O30:T30"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="I35:N35"/>
-    <mergeCell ref="O35:T35"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="I36:N36"/>
-    <mergeCell ref="O36:T36"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="I33:N33"/>
-    <mergeCell ref="O33:T33"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="I34:N34"/>
-    <mergeCell ref="O34:T34"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="I39:N39"/>
-    <mergeCell ref="O39:T39"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="I40:N40"/>
-    <mergeCell ref="O40:T40"/>
-    <mergeCell ref="B37:H37"/>
-    <mergeCell ref="I37:N37"/>
-    <mergeCell ref="O37:T37"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="I38:N38"/>
-    <mergeCell ref="O38:T38"/>
-    <mergeCell ref="B43:H43"/>
-    <mergeCell ref="I43:N43"/>
-    <mergeCell ref="O43:T43"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="K45:M45"/>
-    <mergeCell ref="O45:Q45"/>
-    <mergeCell ref="S45:T45"/>
-    <mergeCell ref="B41:H41"/>
-    <mergeCell ref="I41:N41"/>
-    <mergeCell ref="O41:T41"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="I42:N42"/>
-    <mergeCell ref="O42:T42"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="K54:M54"/>
+    <mergeCell ref="O54:Q54"/>
+    <mergeCell ref="S54:T54"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="K51:M51"/>
+    <mergeCell ref="O51:Q51"/>
+    <mergeCell ref="S51:T51"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="K53:M53"/>
+    <mergeCell ref="O53:Q53"/>
+    <mergeCell ref="S53:T53"/>
     <mergeCell ref="H49:I49"/>
     <mergeCell ref="K49:M49"/>
     <mergeCell ref="O49:Q49"/>
@@ -2227,18 +2134,111 @@
     <mergeCell ref="K48:M48"/>
     <mergeCell ref="O48:Q48"/>
     <mergeCell ref="S48:T48"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="O54:Q54"/>
-    <mergeCell ref="S54:T54"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="K51:M51"/>
-    <mergeCell ref="O51:Q51"/>
-    <mergeCell ref="S51:T51"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="K53:M53"/>
-    <mergeCell ref="O53:Q53"/>
-    <mergeCell ref="S53:T53"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="I43:N43"/>
+    <mergeCell ref="O43:T43"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="K45:M45"/>
+    <mergeCell ref="O45:Q45"/>
+    <mergeCell ref="S45:T45"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="I41:N41"/>
+    <mergeCell ref="O41:T41"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="I42:N42"/>
+    <mergeCell ref="O42:T42"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="I39:N39"/>
+    <mergeCell ref="O39:T39"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="I40:N40"/>
+    <mergeCell ref="O40:T40"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="I37:N37"/>
+    <mergeCell ref="O37:T37"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="I38:N38"/>
+    <mergeCell ref="O38:T38"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="I35:N35"/>
+    <mergeCell ref="O35:T35"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="I36:N36"/>
+    <mergeCell ref="O36:T36"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="I33:N33"/>
+    <mergeCell ref="O33:T33"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="I34:N34"/>
+    <mergeCell ref="O34:T34"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="I31:N31"/>
+    <mergeCell ref="O31:T31"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="I32:N32"/>
+    <mergeCell ref="O32:T32"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="I29:N29"/>
+    <mergeCell ref="O29:T29"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="O30:T30"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="I27:N27"/>
+    <mergeCell ref="O27:T27"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="I28:N28"/>
+    <mergeCell ref="O28:T28"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="I25:N25"/>
+    <mergeCell ref="O25:T25"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="I26:N26"/>
+    <mergeCell ref="O26:T26"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="I23:N23"/>
+    <mergeCell ref="O23:T23"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="I24:N24"/>
+    <mergeCell ref="O24:T24"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="I21:N21"/>
+    <mergeCell ref="O21:T21"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="I22:N22"/>
+    <mergeCell ref="O22:T22"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="I19:N19"/>
+    <mergeCell ref="O19:T19"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="I20:N20"/>
+    <mergeCell ref="O20:T20"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="I17:N17"/>
+    <mergeCell ref="O17:T17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="I18:N18"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="I16:N16"/>
+    <mergeCell ref="O16:T16"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="O13:T13"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="I14:N14"/>
+    <mergeCell ref="O14:T14"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="I11:N11"/>
+    <mergeCell ref="O11:T11"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="I12:N12"/>
+    <mergeCell ref="O12:T12"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="I15:N15"/>
+    <mergeCell ref="O15:T15"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" fitToHeight="0" orientation="portrait" r:id="rId1"/>
